--- a/testng-hybrid-selenium-framwork/src/test/resources/testdata/ParabankRegistraionData.xlsx
+++ b/testng-hybrid-selenium-framwork/src/test/resources/testdata/ParabankRegistraionData.xlsx
@@ -1,33 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Chandan\New Project\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B103C38-D719-44C6-A7F2-CE98DE811713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{33289F23-D4A0-4C2C-91E0-43DE7AF7F5A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4125" yWindow="2295" windowWidth="21600" windowHeight="11295" xr2:uid="{E66005CC-7BC7-4FDD-BFA8-AD6ABBF0C4FC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E66005CC-7BC7-4FDD-BFA8-AD6ABBF0C4FC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -36,12 +23,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
   <si>
-    <t>First Name</t>
-  </si>
-  <si>
-    <t>Last Name</t>
-  </si>
-  <si>
     <t>Address</t>
   </si>
   <si>
@@ -51,12 +32,6 @@
     <t>State</t>
   </si>
   <si>
-    <t>Zip Code</t>
-  </si>
-  <si>
-    <t>Phone </t>
-  </si>
-  <si>
     <t>SSN</t>
   </si>
   <si>
@@ -66,9 +41,6 @@
     <t>Password</t>
   </si>
   <si>
-    <t>Confirm</t>
-  </si>
-  <si>
     <t>Chandan</t>
   </si>
   <si>
@@ -88,6 +60,21 @@
   </si>
   <si>
     <t>Chandan@2</t>
+  </si>
+  <si>
+    <t>First_Name</t>
+  </si>
+  <si>
+    <t>Last_Name</t>
+  </si>
+  <si>
+    <t>Zip_Code</t>
+  </si>
+  <si>
+    <t>Phone_Number</t>
+  </si>
+  <si>
+    <t>Confirm_Password</t>
   </si>
 </sst>
 </file>
@@ -486,62 +473,62 @@
     <col min="8" max="8" width="15.7109375" customWidth="1"/>
     <col min="9" max="9" width="18.140625" customWidth="1"/>
     <col min="10" max="10" width="14.5703125" customWidth="1"/>
-    <col min="11" max="11" width="14.140625" customWidth="1"/>
+    <col min="11" max="11" width="17.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="K1" s="1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>700102</v>
+        <v>12345</v>
       </c>
       <c r="G2">
         <v>7975762194</v>
@@ -550,13 +537,13 @@
         <v>1245</v>
       </c>
       <c r="I2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
